--- a/www/terminologies/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,13 +358,37 @@
     <t>47</t>
   </si>
   <si>
-    <t>Centre expert Parkinson</t>
+    <t>Centre expert maladie de Parkinson</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Agrément Fédération Européenne des Services d'Urgence de la Main (FESUM) - SOS mains</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Centre de Traitement des Brûlés (CTB)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Réseau France Santé</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -699,7 +723,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1028,18 +1052,50 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B42" t="s" s="2">
-        <v>117</v>
+      <c r="B46" t="s" s="2">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,37 +358,13 @@
     <t>47</t>
   </si>
   <si>
-    <t>Centre expert maladie de Parkinson</t>
+    <t>Centre expert Parkinson</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>Agrément Fédération Européenne des Services d'Urgence de la Main (FESUM) - SOS mains</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Centre de Traitement des Brûlés (CTB)</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>Réseau France Santé</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -723,7 +699,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1052,50 +1028,18 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>118</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J227-NiveauExpertise-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -389,6 +389,24 @@
   </si>
   <si>
     <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Centre de Référence d'Infection Ostéo-Articulaire/ Complexes (CRIOA/ C) - Niveau 1 "coordonnateur"</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Centre de Référence d'Infection Ostéo-Articulaire/ Complexes (CRIOA/ C) - Niveau 2 "correspondant"</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Accréditation par la Société Française de Recherche en Médecine du Sommeil (SFRMS)</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R344-NiveauExpertise/FHIR/TRE-R344-NiveauExpertise</t>
@@ -723,7 +741,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1084,18 +1102,42 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>36</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B46" t="s" s="2">
-        <v>125</v>
+      <c r="B49" t="s" s="2">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
